--- a/data/22Juni-Gold_Diggers-v-Towers.xlsx
+++ b/data/22Juni-Gold_Diggers-v-Towers.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R4f97c266313c48f4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rb19e64c4da594a71"/>
   </sheets>
 </workbook>
 </file>
@@ -49,15 +49,12 @@
     <t>VIEVERS NOTES</t>
   </si>
   <si>
+    <t>SCORE</t>
+  </si>
+  <si>
     <t>IFAF</t>
   </si>
   <si>
-    <t>SUP. NOTES</t>
-  </si>
-  <si>
-    <t>PENALTY</t>
-  </si>
-  <si>
     <t>PF-BSB</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>MOD QB A8 - BSB WAIVED</t>
+  </si>
+  <si>
+    <t>U: LUCKY LUKE, SE HELE ACTION FØR WHIPPING IT OUT</t>
   </si>
   <si>
     <t>HCUCLN</t>
@@ -263,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:N148"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -308,9 +308,6 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -328,22 +325,22 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -378,13 +375,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +528,13 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
         <v>24</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -548,13 +545,13 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
         <v>26</v>
-      </c>
-      <c r="D26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -853,25 +850,25 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" t="s">
         <v>28</v>
       </c>
-      <c r="D63" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>29</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>30</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>31</v>
       </c>
-      <c r="H63" t="s">
+      <c r="L63" t="s">
         <v>32</v>
-      </c>
-      <c r="L63" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -882,13 +879,13 @@
         <v>2</v>
       </c>
       <c r="J64" t="s">
+        <v>33</v>
+      </c>
+      <c r="K64" t="s">
         <v>34</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>35</v>
-      </c>
-      <c r="L64" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -899,24 +896,27 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" t="s">
         <v>37</v>
       </c>
-      <c r="E65" t="s">
+      <c r="I65" t="s">
         <v>38</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
+        <v>18</v>
+      </c>
+      <c r="K65" t="s">
         <v>39</v>
       </c>
-      <c r="J65" t="s">
-        <v>19</v>
-      </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>40</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>41</v>
       </c>
     </row>
@@ -928,10 +928,10 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
         <v>42</v>
@@ -1009,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D75" t="s">
         <v>43</v>
@@ -1032,16 +1032,16 @@
         <v>46</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E76" t="s">
         <v>47</v>
       </c>
       <c r="I76" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" t="s">
         <v>18</v>
-      </c>
-      <c r="J76" t="s">
-        <v>19</v>
       </c>
       <c r="L76" t="s">
         <v>48</v>
@@ -1103,19 +1103,19 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E83" t="s">
         <v>49</v>
       </c>
       <c r="I83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L83" t="s">
         <v>50</v>
@@ -1193,10 +1193,10 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
         <v>51</v>
@@ -1205,7 +1205,7 @@
         <v>52</v>
       </c>
       <c r="J92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L92" t="s">
         <v>53</v>
@@ -1235,10 +1235,10 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" t="s">
         <v>21</v>
-      </c>
-      <c r="D95" t="s">
-        <v>22</v>
       </c>
       <c r="E95" t="s">
         <v>54</v>
@@ -1247,7 +1247,7 @@
         <v>52</v>
       </c>
       <c r="J95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L95" t="s">
         <v>55</v>
@@ -1309,10 +1309,10 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
         <v>56</v>
@@ -1321,7 +1321,7 @@
         <v>52</v>
       </c>
       <c r="J102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L102" t="s">
         <v>57</v>
@@ -1362,7 +1362,7 @@
         <v>58</v>
       </c>
       <c r="D106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -1371,13 +1371,13 @@
         <v>60</v>
       </c>
       <c r="G106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
         <v>61</v>
       </c>
       <c r="I106" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L106" t="s">
         <v>62</v>
@@ -1423,10 +1423,10 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E111" t="s">
         <v>51</v>
@@ -1435,13 +1435,13 @@
         <v>58</v>
       </c>
       <c r="G111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H111" t="s">
         <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L111" t="s">
         <v>64</v>
@@ -1466,13 +1466,13 @@
         <v>65</v>
       </c>
       <c r="D113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E113" t="s">
         <v>66</v>
       </c>
       <c r="I113" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L113" t="s">
         <v>67</v>
@@ -1513,13 +1513,13 @@
         <v>68</v>
       </c>
       <c r="D117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E117" t="s">
         <v>69</v>
       </c>
       <c r="I117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L117" t="s">
         <v>70</v>
@@ -1541,22 +1541,22 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
         <v>71</v>
       </c>
       <c r="I119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L119" t="s">
         <v>72</v>
@@ -1594,7 +1594,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D123" t="s">
         <v>73</v>
@@ -1606,10 +1606,10 @@
         <v>52</v>
       </c>
       <c r="J123" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L123" t="s">
         <v>75</v>
@@ -1682,16 +1682,16 @@
         <v>76</v>
       </c>
       <c r="D131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E131" t="s">
         <v>71</v>
       </c>
       <c r="I131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J131" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K131" t="s">
         <v>76</v>
@@ -1711,10 +1711,10 @@
         <v>76</v>
       </c>
       <c r="D132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J132" t="s">
         <v>78</v>
@@ -1742,19 +1742,19 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E134" t="s">
         <v>51</v>
       </c>
       <c r="I134" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J134" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L134" t="s">
         <v>80</v>
@@ -1864,28 +1864,28 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E147" t="s">
         <v>71</v>
       </c>
       <c r="G147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H147" t="s">
         <v>71</v>
       </c>
       <c r="I147" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J147" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K147" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L147" t="s">
         <v>81</v>

--- a/data/22Juni-Gold_Diggers-v-Towers.xlsx
+++ b/data/22Juni-Gold_Diggers-v-Towers.xlsx
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:N148"/>
   <sheetData>
     <row r="1">
@@ -380,8 +380,10 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
-        <v>22</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DCUC</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -855,8 +857,10 @@
       <c r="D63" t="s">
         <v>21</v>
       </c>
-      <c r="E63" t="s">
-        <v>28</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UCDN</t>
+        </is>
       </c>
       <c r="F63" t="s">
         <v>29</v>
@@ -933,8 +937,10 @@
       <c r="D66" t="s">
         <v>21</v>
       </c>
-      <c r="E66" t="s">
-        <v>42</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DCUCLN</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1198,8 +1204,10 @@
       <c r="D92" t="s">
         <v>21</v>
       </c>
-      <c r="E92" t="s">
-        <v>51</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I92" t="s">
         <v>52</v>
@@ -1428,8 +1436,10 @@
       <c r="D111" t="s">
         <v>21</v>
       </c>
-      <c r="E111" t="s">
-        <v>51</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="F111" t="s">
         <v>58</v>
@@ -1515,8 +1525,10 @@
       <c r="D117" t="s">
         <v>21</v>
       </c>
-      <c r="E117" t="s">
-        <v>69</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>DCBC</t>
+        </is>
       </c>
       <c r="I117" t="s">
         <v>38</v>
@@ -1747,8 +1759,10 @@
       <c r="D134" t="s">
         <v>21</v>
       </c>
-      <c r="E134" t="s">
-        <v>51</v>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I134" t="s">
         <v>38</v>
